--- a/AUC_stats.xlsx
+++ b/AUC_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wes/Documents/bps/RP2/cd73_dualantagonist/docking/montpellier-screen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AB89483-4F01-D845-89AE-40A55504F77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D8CED4-F227-E343-B322-111CD8D018C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38200" yWindow="2740" windowWidth="38000" windowHeight="20580" xr2:uid="{7AE26DC2-4DB2-7340-96F1-86A28CD7C8BC}"/>
+    <workbookView xWindow="200" yWindow="800" windowWidth="35440" windowHeight="21380" xr2:uid="{7AE26DC2-4DB2-7340-96F1-86A28CD7C8BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1173,16 +1173,36 @@
       <c r="A26" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
+      <c r="B26" s="2">
+        <v>71.900000000000006</v>
+      </c>
+      <c r="C26" s="2">
+        <v>71</v>
+      </c>
+      <c r="D26" s="2">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="E26" s="2">
+        <v>72.8</v>
+      </c>
+      <c r="F26" s="2">
+        <v>63.1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>71.900000000000006</v>
+      </c>
+      <c r="H26" s="2">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="I26" s="2">
+        <v>72.099999999999994</v>
+      </c>
+      <c r="J26" s="2">
+        <v>73.7</v>
+      </c>
+      <c r="K26" s="2">
+        <v>60.9</v>
+      </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
@@ -1364,6 +1384,36 @@
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>11</v>
+      </c>
+      <c r="B35">
+        <v>11.2</v>
+      </c>
+      <c r="C35">
+        <v>10.9</v>
+      </c>
+      <c r="D35">
+        <v>6.4</v>
+      </c>
+      <c r="E35">
+        <v>10.9</v>
+      </c>
+      <c r="F35">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G35">
+        <v>13.4</v>
+      </c>
+      <c r="H35">
+        <v>13.7</v>
+      </c>
+      <c r="I35">
+        <v>9.9</v>
+      </c>
+      <c r="J35">
+        <v>12.4</v>
+      </c>
+      <c r="K35">
+        <v>2.4</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
@@ -1485,8 +1535,8 @@
       <c r="K57" s="2"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:K8">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="B4:K8 L5">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1498,6 +1548,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:K17">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34:K38">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1509,15 +1571,27 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B34:K38">
+  <conditionalFormatting sqref="B25:K29">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="80"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:K8">
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="80"/>
         <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>

--- a/AUC_stats.xlsx
+++ b/AUC_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wes/Documents/bps/RP2/cd73_dualantagonist/docking/montpellier-screen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D8CED4-F227-E343-B322-111CD8D018C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E567698-E807-D542-8781-96F73DA93CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="200" yWindow="800" windowWidth="35440" windowHeight="21380" xr2:uid="{7AE26DC2-4DB2-7340-96F1-86A28CD7C8BC}"/>
+    <workbookView xWindow="-38200" yWindow="2740" windowWidth="38000" windowHeight="20580" xr2:uid="{7AE26DC2-4DB2-7340-96F1-86A28CD7C8BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -102,7 +102,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -125,6 +125,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -333,7 +340,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -368,6 +375,7 @@
     <xf numFmtId="0" fontId="2" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -785,6 +793,36 @@
       <c r="A5" t="s">
         <v>11</v>
       </c>
+      <c r="B5">
+        <v>57.7</v>
+      </c>
+      <c r="C5">
+        <v>61.7</v>
+      </c>
+      <c r="D5">
+        <v>53.2</v>
+      </c>
+      <c r="E5">
+        <v>60.1</v>
+      </c>
+      <c r="F5">
+        <v>60</v>
+      </c>
+      <c r="G5">
+        <v>61</v>
+      </c>
+      <c r="H5">
+        <v>60.4</v>
+      </c>
+      <c r="I5">
+        <v>54.9</v>
+      </c>
+      <c r="J5">
+        <v>60.8</v>
+      </c>
+      <c r="K5">
+        <v>46.8</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -966,6 +1004,36 @@
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>11</v>
+      </c>
+      <c r="B14">
+        <v>2.9</v>
+      </c>
+      <c r="C14">
+        <v>4.7</v>
+      </c>
+      <c r="D14">
+        <v>-0.6</v>
+      </c>
+      <c r="E14">
+        <v>3.6</v>
+      </c>
+      <c r="F14">
+        <v>2.7</v>
+      </c>
+      <c r="G14">
+        <v>4.3</v>
+      </c>
+      <c r="H14">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I14">
+        <v>0.1</v>
+      </c>
+      <c r="J14">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="K14">
+        <v>-2.7</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -1177,31 +1245,31 @@
         <v>71.900000000000006</v>
       </c>
       <c r="C26" s="2">
-        <v>71</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="D26" s="2">
-        <v>66.099999999999994</v>
+        <v>66.7</v>
       </c>
       <c r="E26" s="2">
-        <v>72.8</v>
+        <v>73.5</v>
       </c>
       <c r="F26" s="2">
-        <v>63.1</v>
+        <v>64.5</v>
       </c>
       <c r="G26" s="2">
-        <v>71.900000000000006</v>
+        <v>73.5</v>
       </c>
       <c r="H26" s="2">
-        <v>72.400000000000006</v>
+        <v>72.099999999999994</v>
       </c>
       <c r="I26" s="2">
-        <v>72.099999999999994</v>
+        <v>71.8</v>
       </c>
       <c r="J26" s="2">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="K26" s="2">
-        <v>60.9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
@@ -1313,6 +1381,7 @@
       <c r="A31" t="s">
         <v>18</v>
       </c>
+      <c r="I31" s="34"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
@@ -1386,34 +1455,34 @@
         <v>11</v>
       </c>
       <c r="B35">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="C35">
-        <v>10.9</v>
+        <v>12.1</v>
       </c>
       <c r="D35">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="E35">
-        <v>10.9</v>
+        <v>12.8</v>
       </c>
       <c r="F35">
-        <v>5.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="G35">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="H35">
-        <v>13.7</v>
+        <v>14.9</v>
       </c>
       <c r="I35">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="K35">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">

--- a/AUC_stats.xlsx
+++ b/AUC_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wes/Documents/bps/RP2/cd73_dualantagonist/docking/montpellier-screen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E567698-E807-D542-8781-96F73DA93CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5ED6D25-94D9-6E4B-A1D3-0F5E40C0210E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38200" yWindow="2740" windowWidth="38000" windowHeight="20580" xr2:uid="{7AE26DC2-4DB2-7340-96F1-86A28CD7C8BC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="21">
   <si>
     <t>4H2I_C_1</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>bootstrap logAUC true actives (57) vs true inactives (84)</t>
+  </si>
+  <si>
+    <t>g543_2_23Jun</t>
+  </si>
+  <si>
+    <t>g543_3_23Jun</t>
   </si>
 </sst>
 </file>
@@ -711,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29978F40-8B5A-7341-B093-8C2B66D41432}">
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.1640625" customWidth="1"/>
@@ -826,785 +832,955 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B6">
-        <v>58.7</v>
+        <v>61.8</v>
       </c>
       <c r="C6">
-        <v>66.2</v>
+        <v>61.5</v>
       </c>
       <c r="D6">
-        <v>45.8</v>
+        <v>55.9</v>
       </c>
       <c r="E6">
-        <v>68.5</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="F6">
-        <v>47.5</v>
+        <v>49.7</v>
       </c>
       <c r="G6">
-        <v>65.400000000000006</v>
+        <v>66.7</v>
       </c>
       <c r="H6">
-        <v>68.2</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="I6">
-        <v>62.6</v>
+        <v>60.2</v>
       </c>
       <c r="J6">
-        <v>65</v>
+        <v>65.8</v>
       </c>
       <c r="K6">
-        <v>46.8</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>57.8</v>
-      </c>
-      <c r="C7">
-        <v>61.5</v>
-      </c>
-      <c r="D7">
-        <v>54.1</v>
-      </c>
-      <c r="E7">
-        <v>61.6</v>
-      </c>
-      <c r="F7">
-        <v>49.5</v>
-      </c>
-      <c r="G7">
-        <v>63.9</v>
-      </c>
-      <c r="H7">
-        <v>66.5</v>
-      </c>
-      <c r="I7">
-        <v>59</v>
-      </c>
-      <c r="J7">
-        <v>63</v>
-      </c>
-      <c r="K7">
-        <v>47.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8">
-        <v>59.2</v>
+        <v>58.7</v>
       </c>
       <c r="C8">
-        <v>60.4</v>
+        <v>66.2</v>
       </c>
       <c r="D8">
-        <v>51.9</v>
+        <v>45.8</v>
       </c>
       <c r="E8">
-        <v>66.8</v>
+        <v>68.5</v>
       </c>
       <c r="F8">
-        <v>52.7</v>
+        <v>47.5</v>
       </c>
       <c r="G8">
-        <v>66.3</v>
+        <v>65.400000000000006</v>
       </c>
       <c r="H8">
-        <v>64.400000000000006</v>
+        <v>68.2</v>
       </c>
       <c r="I8">
-        <v>59.2</v>
+        <v>62.6</v>
       </c>
       <c r="J8">
-        <v>62.1</v>
+        <v>65</v>
       </c>
       <c r="K8">
-        <v>46</v>
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>57.8</v>
+      </c>
+      <c r="C9">
+        <v>61.5</v>
+      </c>
+      <c r="D9">
+        <v>54.1</v>
+      </c>
+      <c r="E9">
+        <v>61.6</v>
+      </c>
+      <c r="F9">
+        <v>49.5</v>
+      </c>
+      <c r="G9">
+        <v>63.9</v>
+      </c>
+      <c r="H9">
+        <v>66.5</v>
+      </c>
+      <c r="I9">
+        <v>59</v>
+      </c>
+      <c r="J9">
+        <v>63</v>
+      </c>
+      <c r="K9">
+        <v>47.3</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>59.2</v>
+      </c>
+      <c r="C10">
+        <v>60.4</v>
+      </c>
+      <c r="D10">
+        <v>51.9</v>
+      </c>
+      <c r="E10">
+        <v>66.8</v>
+      </c>
+      <c r="F10">
+        <v>52.7</v>
+      </c>
+      <c r="G10">
+        <v>66.3</v>
+      </c>
+      <c r="H10">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="I10">
+        <v>59.2</v>
+      </c>
+      <c r="J10">
+        <v>62.1</v>
+      </c>
+      <c r="K10">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
         <v>0</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C14" t="s">
         <v>1</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D14" t="s">
         <v>3</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E14" t="s">
         <v>2</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F14" t="s">
         <v>4</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G14" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I14" t="s">
         <v>7</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J14" t="s">
         <v>8</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K14" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13">
-        <v>2.8</v>
-      </c>
-      <c r="C13">
-        <v>4.8</v>
-      </c>
-      <c r="D13">
-        <v>0.5</v>
-      </c>
-      <c r="E13">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F13">
-        <v>1.5</v>
-      </c>
-      <c r="G13">
-        <v>5.2</v>
-      </c>
-      <c r="H13">
-        <v>5.3</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
-      <c r="J13">
-        <v>4.5</v>
-      </c>
-      <c r="K13">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14">
-        <v>2.9</v>
-      </c>
-      <c r="C14">
-        <v>4.7</v>
-      </c>
-      <c r="D14">
-        <v>-0.6</v>
-      </c>
-      <c r="E14">
-        <v>3.6</v>
-      </c>
-      <c r="F14">
-        <v>2.7</v>
-      </c>
-      <c r="G14">
-        <v>4.3</v>
-      </c>
-      <c r="H14">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="I14">
-        <v>0.1</v>
-      </c>
-      <c r="J14">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="K14">
-        <v>-2.7</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B15">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="C15">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="D15">
-        <v>-1.6</v>
+        <v>0.5</v>
       </c>
       <c r="E15">
-        <v>8.1999999999999993</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F15">
-        <v>-1.9</v>
+        <v>1.5</v>
       </c>
       <c r="G15">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="H15">
-        <v>7.7</v>
+        <v>5.3</v>
       </c>
       <c r="I15">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="K15">
-        <v>-1.9</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B16">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="C16">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="D16">
-        <v>0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="E16">
-        <v>6.1</v>
+        <v>3.6</v>
       </c>
       <c r="F16">
-        <v>-1.7</v>
+        <v>2.7</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="H16">
-        <v>7.8</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I16">
-        <v>2.8</v>
+        <v>0.1</v>
       </c>
       <c r="J16">
-        <v>4.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="K16">
-        <v>-1.7</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>3.5</v>
+      </c>
+      <c r="D17">
+        <v>2.1</v>
+      </c>
+      <c r="E17">
+        <v>5.8</v>
+      </c>
+      <c r="F17">
+        <v>-1</v>
+      </c>
+      <c r="G17">
+        <v>8.1</v>
+      </c>
+      <c r="H17">
+        <v>4.8</v>
+      </c>
+      <c r="I17">
+        <v>2.7</v>
+      </c>
+      <c r="J17">
+        <v>6.1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19">
+        <v>3.1</v>
+      </c>
+      <c r="C19">
+        <v>6.7</v>
+      </c>
+      <c r="D19">
+        <v>-1.6</v>
+      </c>
+      <c r="E19">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F19">
+        <v>-1.9</v>
+      </c>
+      <c r="G19">
+        <v>6.6</v>
+      </c>
+      <c r="H19">
+        <v>7.7</v>
+      </c>
+      <c r="I19">
+        <v>3.7</v>
+      </c>
+      <c r="J19">
+        <v>5.7</v>
+      </c>
+      <c r="K19">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20">
+        <v>1.9</v>
+      </c>
+      <c r="C20">
+        <v>3.9</v>
+      </c>
+      <c r="D20">
+        <v>0.8</v>
+      </c>
+      <c r="E20">
+        <v>6.1</v>
+      </c>
+      <c r="F20">
+        <v>-1.7</v>
+      </c>
+      <c r="G20">
+        <v>6</v>
+      </c>
+      <c r="H20">
+        <v>7.8</v>
+      </c>
+      <c r="I20">
+        <v>2.8</v>
+      </c>
+      <c r="J20">
+        <v>4.7</v>
+      </c>
+      <c r="K20">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>14</v>
       </c>
-      <c r="B17">
+      <c r="B21">
         <v>3.9</v>
       </c>
-      <c r="C17">
+      <c r="C21">
         <v>3.9</v>
       </c>
-      <c r="D17">
+      <c r="D21">
         <v>-0.1</v>
       </c>
-      <c r="E17">
+      <c r="E21">
         <v>5.7</v>
       </c>
-      <c r="F17">
+      <c r="F21">
         <v>-0.1</v>
       </c>
-      <c r="G17">
+      <c r="G21">
         <v>7</v>
       </c>
-      <c r="H17">
+      <c r="H21">
         <v>6.1</v>
       </c>
-      <c r="I17">
+      <c r="I21">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J17">
+      <c r="J21">
         <v>5.5</v>
       </c>
-      <c r="K17">
+      <c r="K21">
         <v>-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="3">
-        <v>69.8</v>
-      </c>
-      <c r="C25" s="4">
-        <v>73.5</v>
-      </c>
-      <c r="D25" s="5">
-        <v>66.400000000000006</v>
-      </c>
-      <c r="E25" s="6">
-        <v>70.5</v>
-      </c>
-      <c r="F25" s="7">
-        <v>64.900000000000006</v>
-      </c>
-      <c r="G25" s="8">
-        <v>73</v>
-      </c>
-      <c r="H25" s="9">
-        <v>73.7</v>
-      </c>
-      <c r="I25" s="10">
-        <v>71.8</v>
-      </c>
-      <c r="J25" s="11">
-        <v>72.3</v>
-      </c>
-      <c r="K25" s="12">
-        <v>56.3</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" s="2">
-        <v>71.900000000000006</v>
-      </c>
-      <c r="C26" s="2">
-        <v>70.900000000000006</v>
-      </c>
-      <c r="D26" s="2">
-        <v>66.7</v>
-      </c>
-      <c r="E26" s="2">
-        <v>73.5</v>
-      </c>
-      <c r="F26" s="2">
-        <v>64.5</v>
-      </c>
-      <c r="G26" s="2">
-        <v>73.5</v>
-      </c>
-      <c r="H26" s="2">
-        <v>72.099999999999994</v>
-      </c>
-      <c r="I26" s="2">
-        <v>71.8</v>
-      </c>
-      <c r="J26" s="2">
-        <v>74.5</v>
-      </c>
-      <c r="K26" s="2">
-        <v>60</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B27" s="13">
-        <v>66.099999999999994</v>
-      </c>
-      <c r="C27" s="14">
-        <v>68.900000000000006</v>
-      </c>
-      <c r="D27" s="15">
-        <v>45.2</v>
-      </c>
-      <c r="E27" s="16">
-        <v>69</v>
-      </c>
-      <c r="F27" s="17">
-        <v>47.7</v>
-      </c>
-      <c r="G27" s="18">
-        <v>67.599999999999994</v>
-      </c>
-      <c r="H27" s="19">
-        <v>69.900000000000006</v>
-      </c>
-      <c r="I27" s="20">
-        <v>69.2</v>
-      </c>
-      <c r="J27" s="21">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="K27" s="22">
-        <v>40.4</v>
-      </c>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" s="19">
-        <v>69.900000000000006</v>
-      </c>
-      <c r="C28" s="23">
-        <v>67.900000000000006</v>
-      </c>
-      <c r="D28" s="24">
-        <v>62.9</v>
-      </c>
-      <c r="E28" s="25">
-        <v>68.8</v>
-      </c>
-      <c r="F28" s="26">
-        <v>59.3</v>
-      </c>
-      <c r="G28" s="8">
-        <v>73</v>
-      </c>
-      <c r="H28" s="27">
-        <v>74.400000000000006</v>
-      </c>
-      <c r="I28" s="28">
-        <v>71.7</v>
-      </c>
-      <c r="J28" s="29">
-        <v>71.599999999999994</v>
-      </c>
-      <c r="K28" s="30">
-        <v>53.1</v>
+      <c r="A28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="3">
+        <v>69.8</v>
+      </c>
+      <c r="C29" s="4">
+        <v>73.5</v>
+      </c>
+      <c r="D29" s="5">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="E29" s="6">
+        <v>70.5</v>
+      </c>
+      <c r="F29" s="7">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="G29" s="8">
+        <v>73</v>
+      </c>
+      <c r="H29" s="9">
+        <v>73.7</v>
+      </c>
+      <c r="I29" s="10">
+        <v>71.8</v>
+      </c>
+      <c r="J29" s="11">
+        <v>72.3</v>
+      </c>
+      <c r="K29" s="12">
+        <v>56.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="2">
+        <v>71.900000000000006</v>
+      </c>
+      <c r="C30" s="2">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="D30" s="2">
+        <v>66.7</v>
+      </c>
+      <c r="E30" s="2">
+        <v>73.5</v>
+      </c>
+      <c r="F30" s="2">
+        <v>64.5</v>
+      </c>
+      <c r="G30" s="2">
+        <v>73.5</v>
+      </c>
+      <c r="H30" s="2">
+        <v>72.099999999999994</v>
+      </c>
+      <c r="I30" s="2">
+        <v>71.8</v>
+      </c>
+      <c r="J30" s="2">
+        <v>74.5</v>
+      </c>
+      <c r="K30" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="2">
+        <v>67.8</v>
+      </c>
+      <c r="C31" s="2">
+        <v>71.099999999999994</v>
+      </c>
+      <c r="D31" s="2">
+        <v>56.6</v>
+      </c>
+      <c r="E31" s="2">
+        <v>71.3</v>
+      </c>
+      <c r="F31" s="2">
+        <v>52.2</v>
+      </c>
+      <c r="G31" s="2">
+        <v>72</v>
+      </c>
+      <c r="H31" s="2">
+        <v>69.5</v>
+      </c>
+      <c r="I31" s="2">
+        <v>72</v>
+      </c>
+      <c r="J31" s="2">
+        <v>71.599999999999994</v>
+      </c>
+      <c r="K31" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="13">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="C33" s="14">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="D33" s="15">
+        <v>45.2</v>
+      </c>
+      <c r="E33" s="16">
+        <v>69</v>
+      </c>
+      <c r="F33" s="17">
+        <v>47.7</v>
+      </c>
+      <c r="G33" s="18">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="H33" s="19">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="I33" s="20">
+        <v>69.2</v>
+      </c>
+      <c r="J33" s="21">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="K33" s="22">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="19">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="C34" s="23">
+        <v>67.900000000000006</v>
+      </c>
+      <c r="D34" s="24">
+        <v>62.9</v>
+      </c>
+      <c r="E34" s="25">
+        <v>68.8</v>
+      </c>
+      <c r="F34" s="26">
+        <v>59.3</v>
+      </c>
+      <c r="G34" s="8">
+        <v>73</v>
+      </c>
+      <c r="H34" s="27">
+        <v>74.400000000000006</v>
+      </c>
+      <c r="I34" s="28">
+        <v>71.7</v>
+      </c>
+      <c r="J34" s="29">
+        <v>71.599999999999994</v>
+      </c>
+      <c r="K34" s="30">
+        <v>53.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B35" s="23">
         <v>68.099999999999994</v>
       </c>
-      <c r="C29" s="13">
+      <c r="C35" s="13">
         <v>66.099999999999994</v>
       </c>
-      <c r="D29" s="26">
+      <c r="D35" s="26">
         <v>58.9</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E35" s="3">
         <v>69.8</v>
       </c>
-      <c r="F29" s="31">
+      <c r="F35" s="31">
         <v>62.7</v>
       </c>
-      <c r="G29" s="32">
+      <c r="G35" s="32">
         <v>71.099999999999994</v>
       </c>
-      <c r="H29" s="18">
+      <c r="H35" s="18">
         <v>67.8</v>
       </c>
-      <c r="I29" s="5">
+      <c r="I35" s="5">
         <v>66.5</v>
       </c>
-      <c r="J29" s="23">
+      <c r="J35" s="23">
         <v>68</v>
       </c>
-      <c r="K29" s="33">
+      <c r="K35" s="33">
         <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>18</v>
-      </c>
-      <c r="I31" s="34"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" t="s">
-        <v>1</v>
-      </c>
-      <c r="D33" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" t="s">
-        <v>2</v>
-      </c>
-      <c r="F33" t="s">
-        <v>4</v>
-      </c>
-      <c r="G33" t="s">
-        <v>5</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I33" t="s">
-        <v>7</v>
-      </c>
-      <c r="J33" t="s">
-        <v>8</v>
-      </c>
-      <c r="K33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>10</v>
-      </c>
-      <c r="B34">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="C34">
-        <v>12.3</v>
-      </c>
-      <c r="D34">
-        <v>7.2</v>
-      </c>
-      <c r="E34">
-        <v>12.3</v>
-      </c>
-      <c r="F34">
-        <v>5.6</v>
-      </c>
-      <c r="G34">
-        <v>13.2</v>
-      </c>
-      <c r="H34">
-        <v>14.3</v>
-      </c>
-      <c r="I34">
-        <v>8.4</v>
-      </c>
-      <c r="J34">
-        <v>10.6</v>
-      </c>
-      <c r="K34">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>11</v>
-      </c>
-      <c r="B35">
-        <v>10.9</v>
-      </c>
-      <c r="C35">
-        <v>12.1</v>
-      </c>
-      <c r="D35">
-        <v>6.3</v>
-      </c>
-      <c r="E35">
-        <v>12.8</v>
-      </c>
-      <c r="F35">
-        <v>4.3</v>
-      </c>
-      <c r="G35">
-        <v>13.3</v>
-      </c>
-      <c r="H35">
-        <v>14.9</v>
-      </c>
-      <c r="I35">
-        <v>9</v>
-      </c>
-      <c r="J35">
-        <v>12</v>
-      </c>
-      <c r="K35">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36">
-        <v>6.8</v>
-      </c>
-      <c r="C36">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="D36">
-        <v>0.6</v>
-      </c>
-      <c r="E36">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="F36">
-        <v>-1</v>
-      </c>
-      <c r="G36">
-        <v>10.1</v>
-      </c>
-      <c r="H36">
-        <v>11.2</v>
-      </c>
-      <c r="I36">
-        <v>9</v>
-      </c>
-      <c r="J36">
-        <v>8.4</v>
-      </c>
-      <c r="K36">
-        <v>-2</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="34"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" t="s">
+        <v>3</v>
+      </c>
+      <c r="E39" t="s">
+        <v>2</v>
+      </c>
+      <c r="F39" t="s">
+        <v>4</v>
+      </c>
+      <c r="G39" t="s">
+        <v>5</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I39" t="s">
+        <v>7</v>
+      </c>
+      <c r="J39" t="s">
+        <v>8</v>
+      </c>
+      <c r="K39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>10</v>
+      </c>
+      <c r="B40">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="C40">
+        <v>12.3</v>
+      </c>
+      <c r="D40">
+        <v>7.2</v>
+      </c>
+      <c r="E40">
+        <v>12.3</v>
+      </c>
+      <c r="F40">
+        <v>5.6</v>
+      </c>
+      <c r="G40">
+        <v>13.2</v>
+      </c>
+      <c r="H40">
+        <v>14.3</v>
+      </c>
+      <c r="I40">
+        <v>8.4</v>
+      </c>
+      <c r="J40">
+        <v>10.6</v>
+      </c>
+      <c r="K40">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41">
+        <v>10.9</v>
+      </c>
+      <c r="C41">
+        <v>12.1</v>
+      </c>
+      <c r="D41">
+        <v>6.3</v>
+      </c>
+      <c r="E41">
+        <v>12.8</v>
+      </c>
+      <c r="F41">
+        <v>4.3</v>
+      </c>
+      <c r="G41">
+        <v>13.3</v>
+      </c>
+      <c r="H41">
+        <v>14.9</v>
+      </c>
+      <c r="I41">
+        <v>9</v>
+      </c>
+      <c r="J41">
+        <v>12</v>
+      </c>
+      <c r="K41">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="C42">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="D42">
+        <v>3.2</v>
+      </c>
+      <c r="E42">
+        <v>8.6</v>
+      </c>
+      <c r="F42">
+        <v>1.7</v>
+      </c>
+      <c r="G42">
+        <v>12.1</v>
+      </c>
+      <c r="H42">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="I42">
+        <v>9.4</v>
+      </c>
+      <c r="J42">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="K42">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44">
+        <v>6.8</v>
+      </c>
+      <c r="C44">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="D44">
+        <v>0.6</v>
+      </c>
+      <c r="E44">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="F44">
+        <v>-1</v>
+      </c>
+      <c r="G44">
+        <v>10.1</v>
+      </c>
+      <c r="H44">
+        <v>11.2</v>
+      </c>
+      <c r="I44">
+        <v>9</v>
+      </c>
+      <c r="J44">
+        <v>8.4</v>
+      </c>
+      <c r="K44">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
         <v>13</v>
       </c>
-      <c r="B37">
+      <c r="B45">
         <v>9.6</v>
       </c>
-      <c r="C37">
+      <c r="C45">
         <v>7.7</v>
       </c>
-      <c r="D37">
+      <c r="D45">
         <v>4.4000000000000004</v>
       </c>
-      <c r="E37">
+      <c r="E45">
         <v>11.1</v>
       </c>
-      <c r="F37">
+      <c r="F45">
         <v>4.7</v>
       </c>
-      <c r="G37">
+      <c r="G45">
         <v>11.4</v>
       </c>
-      <c r="H37">
+      <c r="H45">
         <v>13.9</v>
       </c>
-      <c r="I37">
+      <c r="I45">
         <v>7.7</v>
       </c>
-      <c r="J37">
+      <c r="J45">
         <v>11.2</v>
       </c>
-      <c r="K37">
+      <c r="K45">
         <v>0.6</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
         <v>14</v>
       </c>
-      <c r="B38">
+      <c r="B46">
         <v>7.4</v>
       </c>
-      <c r="C38">
+      <c r="C46">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D38">
+      <c r="D46">
         <v>3.6</v>
       </c>
-      <c r="E38">
+      <c r="E46">
         <v>8.6999999999999993</v>
       </c>
-      <c r="F38">
+      <c r="F46">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G38">
+      <c r="G46">
         <v>10.9</v>
       </c>
-      <c r="H38">
+      <c r="H46">
         <v>8.4</v>
       </c>
-      <c r="I38">
+      <c r="I46">
         <v>7.3</v>
       </c>
-      <c r="J38">
+      <c r="J46">
         <v>8.8000000000000007</v>
       </c>
-      <c r="K38">
+      <c r="K46">
         <v>-0.8</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:K8 L5">
+  <conditionalFormatting sqref="B4:K10 L5:L7">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1616,7 +1792,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13:K17">
+  <conditionalFormatting sqref="B15:K21">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1628,7 +1804,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B34:K38">
+  <conditionalFormatting sqref="B40:K46">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1640,7 +1816,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B25:K29">
+  <conditionalFormatting sqref="B29:K35">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1652,7 +1828,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:K8">
+  <conditionalFormatting sqref="B4:K10">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1666,9 +1842,9 @@
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="H3" r:id="rId1" display="6TVE_C_@" xr:uid="{77561480-A1A3-0142-8D0A-C9E5CCFA5804}"/>
-    <hyperlink ref="H12" r:id="rId2" display="6TVE_C_@" xr:uid="{0A740804-6500-4941-B93E-98E80738321B}"/>
-    <hyperlink ref="H33" r:id="rId3" display="6TVE_C_@" xr:uid="{DF95B75E-CBAD-9142-8126-7BD53D2176F1}"/>
-    <hyperlink ref="H24" r:id="rId4" display="mailto:6TVE_C_@" xr:uid="{90C8DFCF-25BA-3941-B24C-37F976EDEEA9}"/>
+    <hyperlink ref="H14" r:id="rId2" display="6TVE_C_@" xr:uid="{0A740804-6500-4941-B93E-98E80738321B}"/>
+    <hyperlink ref="H39" r:id="rId3" display="6TVE_C_@" xr:uid="{DF95B75E-CBAD-9142-8126-7BD53D2176F1}"/>
+    <hyperlink ref="H28" r:id="rId4" display="mailto:6TVE_C_@" xr:uid="{90C8DFCF-25BA-3941-B24C-37F976EDEEA9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/AUC_stats.xlsx
+++ b/AUC_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wes/Documents/bps/RP2/cd73_dualantagonist/docking/montpellier-screen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5ED6D25-94D9-6E4B-A1D3-0F5E40C0210E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABCA4C0-9522-4044-A787-97BFF84B9BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38200" yWindow="2740" windowWidth="38000" windowHeight="20580" xr2:uid="{7AE26DC2-4DB2-7340-96F1-86A28CD7C8BC}"/>
+    <workbookView xWindow="18020" yWindow="800" windowWidth="17620" windowHeight="21380" xr2:uid="{7AE26DC2-4DB2-7340-96F1-86A28CD7C8BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -869,6 +869,36 @@
       <c r="A7" t="s">
         <v>20</v>
       </c>
+      <c r="B7" s="2">
+        <v>59.6</v>
+      </c>
+      <c r="C7" s="2">
+        <v>62</v>
+      </c>
+      <c r="D7" s="2">
+        <v>55.8</v>
+      </c>
+      <c r="E7" s="2">
+        <v>61.2</v>
+      </c>
+      <c r="F7" s="2">
+        <v>58</v>
+      </c>
+      <c r="G7" s="2">
+        <v>63.9</v>
+      </c>
+      <c r="H7" s="2">
+        <v>63.2</v>
+      </c>
+      <c r="I7" s="2">
+        <v>59.4</v>
+      </c>
+      <c r="J7" s="2">
+        <v>59.5</v>
+      </c>
+      <c r="K7" s="2">
+        <v>49.3</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -1120,6 +1150,36 @@
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>4.2</v>
+      </c>
+      <c r="D18">
+        <v>1.8</v>
+      </c>
+      <c r="E18">
+        <v>4.7</v>
+      </c>
+      <c r="F18">
+        <v>1.6</v>
+      </c>
+      <c r="G18">
+        <v>6.4</v>
+      </c>
+      <c r="H18">
+        <v>6</v>
+      </c>
+      <c r="I18">
+        <v>2.6</v>
+      </c>
+      <c r="J18">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="K18">
+        <v>-1</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -1397,16 +1457,36 @@
       <c r="A32" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
+      <c r="B32" s="2">
+        <v>69.5</v>
+      </c>
+      <c r="C32" s="2">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="D32" s="2">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="E32" s="2">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="F32" s="2">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="G32" s="2">
+        <v>75.8</v>
+      </c>
+      <c r="H32" s="2">
+        <v>74.7</v>
+      </c>
+      <c r="I32" s="2">
+        <v>70</v>
+      </c>
+      <c r="J32" s="2">
+        <v>72.5</v>
+      </c>
+      <c r="K32" s="2">
+        <v>55.7</v>
+      </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
@@ -1659,6 +1739,36 @@
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>20</v>
+      </c>
+      <c r="B43">
+        <v>9.5</v>
+      </c>
+      <c r="C43">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="D43">
+        <v>6</v>
+      </c>
+      <c r="E43">
+        <v>11.8</v>
+      </c>
+      <c r="F43">
+        <v>4.8</v>
+      </c>
+      <c r="G43">
+        <v>13.5</v>
+      </c>
+      <c r="H43">
+        <v>13.7</v>
+      </c>
+      <c r="I43">
+        <v>9.9</v>
+      </c>
+      <c r="J43">
+        <v>10.6</v>
+      </c>
+      <c r="K43">
+        <v>1.9</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
@@ -1780,8 +1890,8 @@
       <c r="K65" s="2"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:K10 L5:L7">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="B4:K6 L5:L7 B8:K10">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1792,20 +1902,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B15:K21">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="B4:K6 B8:K10">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
-        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="80"/>
         <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B40:K46">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="B15:K17 B19:K21">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1817,6 +1927,30 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29:K35">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="80"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40:K46">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:K7">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1828,15 +1962,15 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:K10">
+  <conditionalFormatting sqref="B18:K18">
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="num" val="0"/>
+        <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="80"/>
+        <cfvo type="max"/>
         <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>

--- a/AUC_stats.xlsx
+++ b/AUC_stats.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABCA4C0-9522-4044-A787-97BFF84B9BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18020" yWindow="800" windowWidth="17620" windowHeight="21380" xr2:uid="{7AE26DC2-4DB2-7340-96F1-86A28CD7C8BC}"/>
+    <workbookView xWindow="23920" yWindow="800" windowWidth="11720" windowHeight="21380" xr2:uid="{7AE26DC2-4DB2-7340-96F1-86A28CD7C8BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1890,6 +1890,18 @@
       <c r="K65" s="2"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B4:K6 B8:K10">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="80"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B4:K6 L5:L7 B8:K10">
     <cfRule type="colorScale" priority="9">
       <colorScale>
@@ -1902,8 +1914,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:K6 B8:K10">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="B7:K7">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1916,6 +1928,18 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:K17 B19:K21">
     <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18:K18">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1950,30 +1974,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:K7">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="80"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B18:K18">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="H3" r:id="rId1" display="6TVE_C_@" xr:uid="{77561480-A1A3-0142-8D0A-C9E5CCFA5804}"/>
     <hyperlink ref="H14" r:id="rId2" display="6TVE_C_@" xr:uid="{0A740804-6500-4941-B93E-98E80738321B}"/>
